--- a/diseases/d158/2020-2025.xlsx
+++ b/diseases/d158/2020-2025.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20814,7 +20814,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22398,7 +22398,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25170,7 +25170,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
